--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -61,7 +61,9 @@
     <t xml:space="preserve">dialogue_tutorial_1_1_100</t>
   </si>
   <si>
-    <t xml:space="preserve">제 게임에 오신것을 환영합니다, 이 게임은 간략한 플랫포머 게임입니다&lt;np&gt;좌우 방향키로 이동, 스페이스로 점프를 수행할 수 있습니다</t>
+    <t xml:space="preserve">제 게임에 오신것을 환영합니다, 이 게임은 매우 간단한 플랫포머 게임으로, 테스트 빌드에 가깝습니다
+대화창은 마우스로 화면을 클릭해 넘길 수 있습니다&lt;np&gt;좌우 방향키로 이동, 스페이스로 점프를 수행할 수 있습니다
+점프의 경우 꾹 눌러 차징이 가능하며, 차징 도중 윗 방향키나 아래 방향키를 누르면 각도조절을 할 수 있습니다&lt;np&gt;현재 게임은 테스트 단계이기에 마을 우측의 우물로 뛰어들면 게임이 끝납니다</t>
   </si>
   <si>
     <t xml:space="preserve">dialogue_mainstream_1_1_100</t>
@@ -234,7 +236,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -253,6 +255,10 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -526,7 +532,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="112.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="166.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="77.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="51.19"/>
   </cols>
@@ -595,12 +601,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="2"/>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="2"/>
@@ -608,438 +614,438 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7" t="s">
+      <c r="B5" s="8"/>
+      <c r="C5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7" t="s">
+      <c r="B6" s="8"/>
+      <c r="C6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7" t="s">
+      <c r="B7" s="8"/>
+      <c r="C7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7" t="s">
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7" t="s">
+      <c r="B8" s="8"/>
+      <c r="C8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7" t="s">
+      <c r="D8" s="8"/>
+      <c r="E8" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7" t="s">
+      <c r="B9" s="8"/>
+      <c r="C9" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7" t="s">
+      <c r="B10" s="8"/>
+      <c r="C10" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7" t="s">
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7" t="s">
+      <c r="B11" s="8"/>
+      <c r="C11" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
+      <c r="A35" s="9"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
+      <c r="A36" s="9"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
   <si>
     <t xml:space="preserve">고유 ID</t>
   </si>
@@ -58,12 +58,24 @@
     <t xml:space="preserve">VoicePath</t>
   </si>
   <si>
-    <t xml:space="preserve">dialogue_tutorial_1_1_100</t>
+    <t xml:space="preserve">dialogue_tutorial_1_1_001</t>
   </si>
   <si>
     <t xml:space="preserve">제 게임에 오신것을 환영합니다, 이 게임은 매우 간단한 플랫포머 게임으로, 테스트 빌드에 가깝습니다
 대화창은 마우스로 화면을 클릭해 넘길 수 있습니다&lt;np&gt;좌우 방향키로 이동, 스페이스로 점프를 수행할 수 있습니다
-점프의 경우 꾹 눌러 차징이 가능하며, 차징 도중 윗 방향키나 아래 방향키를 누르면 각도조절을 할 수 있습니다&lt;np&gt;현재 게임은 테스트 단계이기에 마을 우측의 우물로 뛰어들면 게임이 끝납니다</t>
+점프의 경우 꾹 눌러 차징이 가능하며, 차징 도중 윗 방향키나 아래 방향키를 누르면 각도조절을 할 수 있습니다&lt;np&gt;현재 게임은 테스트 단계이기에 체력이 모두 줄어들거나, 마을 우측의 우물로 뛰어들면 게임이 끝납니다&lt;np&gt;ESC키를 누를 시 게임이 강제종료 됩니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dialogue_tutorial_1_1_002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이와 같은 표지판 근처에 다가가시면 대화창이 뜹니다&lt;np&gt;앞에 보이는 가시에 닿이면 피해를 입습니다&lt;np&gt;가시 바로 옆 동적 생성된 아이템에 다가가시면 아이템 획득 후 체력이 회복됩니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dialogue_tutorial_1_1_003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이 우물 안으로 들어가시면 게임이 끝납니다</t>
   </si>
   <si>
     <t xml:space="preserve">dialogue_mainstream_1_1_100</t>
@@ -627,21 +639,19 @@
       <c r="S4" s="7"/>
       <c r="T4" s="7"/>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+    <row r="5" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="8"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
@@ -652,22 +662,22 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+    </row>
+    <row r="6" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
@@ -678,22 +688,24 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8" t="s">
+      <c r="G7" s="8" t="s">
         <v>21</v>
       </c>
+      <c r="H7" s="8"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
@@ -707,19 +719,17 @@
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
       <c r="I8" s="6"/>
@@ -735,17 +745,19 @@
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
+      <c r="H9" s="8" t="s">
+        <v>25</v>
+      </c>
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
@@ -759,19 +771,21 @@
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
       <c r="G10" s="8"/>
-      <c r="H10" s="8" t="s">
-        <v>21</v>
-      </c>
+      <c r="H10" s="8"/>
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
@@ -796,21 +810,51 @@
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8"/>
+      <c r="A12" s="8" t="s">
+        <v>32</v>
+      </c>
       <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
+      <c r="C12" s="8" t="s">
+        <v>33</v>
+      </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
+      <c r="H12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6"/>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8"/>
+      <c r="A13" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
+      <c r="C13" s="8" t="s">
+        <v>35</v>
+      </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
@@ -848,24 +892,24 @@
       <c r="H16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="9"/>
@@ -1047,8 +1091,26 @@
       <c r="G36" s="9"/>
       <c r="H36" s="9"/>
     </row>
-    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="9"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+    </row>
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="9"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+    </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2006,8 +2068,8 @@
     <row r="993" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="994" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="995" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="996" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="997" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="38">
   <si>
     <t xml:space="preserve">고유 ID</t>
   </si>
@@ -73,6 +73,12 @@
   </si>
   <si>
     <t xml:space="preserve">dialogue_tutorial_1_1_003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이런 보석의 경우엔 획득 시 도감 UI에 등록됩니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dialogue_tutorial_1_1_004</t>
   </si>
   <si>
     <t xml:space="preserve">이 우물 안으로 들어가시면 게임이 끝납니다</t>
@@ -691,21 +697,19 @@
       <c r="S6" s="7"/>
       <c r="T6" s="7"/>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+    <row r="7" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="2"/>
+      <c r="C7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="8"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
@@ -716,6 +720,8 @@
       <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
       <c r="R7" s="6"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
@@ -723,14 +729,14 @@
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="G8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
       <c r="H8" s="8"/>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
@@ -745,19 +751,19 @@
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="8"/>
+      <c r="D9" s="8" t="s">
+        <v>25</v>
+      </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
-      <c r="H9" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="H9" s="8"/>
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
@@ -771,21 +777,19 @@
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
@@ -799,15 +803,19 @@
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
       <c r="I11" s="6"/>
@@ -833,9 +841,7 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
-      <c r="H12" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="H12" s="8"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
@@ -859,12 +865,28 @@
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
+      <c r="H13" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8"/>
+      <c r="A14" s="8" t="s">
+        <v>36</v>
+      </c>
       <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
+      <c r="C14" s="8" t="s">
+        <v>37</v>
+      </c>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
@@ -912,14 +934,14 @@
       <c r="H18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="9"/>
@@ -1111,7 +1133,16 @@
       <c r="G38" s="9"/>
       <c r="H38" s="9"/>
     </row>
-    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="9"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+    </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2070,7 +2101,7 @@
     <row r="995" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="996" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="997" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="998" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>

--- a/JsonConverter/ExcelFiles/Dialogue.xlsx
+++ b/JsonConverter/ExcelFiles/Dialogue.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">dialogue_tutorial_1_1_004</t>
   </si>
   <si>
-    <t xml:space="preserve">이 우물 안으로 들어가시면 게임이 끝납니다</t>
+    <t xml:space="preserve">이 우물 안으로 들어가시면 게임이 시작됩니다</t>
   </si>
   <si>
     <t xml:space="preserve">dialogue_mainstream_1_1_100</t>
